--- a/output/CS_SFIAFormat/sfiaformat_mapping_cosine_SkillNER YAKE_KeyBERT_CS.xlsx
+++ b/output/CS_SFIAFormat/sfiaformat_mapping_cosine_SkillNER YAKE_KeyBERT_CS.xlsx
@@ -510,16 +510,16 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.2214</v>
+        <v>0.228</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2233</v>
+        <v>0.2299</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2199</v>
+        <v>0.2987</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2109</v>
+        <v>0.2687</v>
       </c>
     </row>
     <row r="5">
@@ -533,7 +533,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0.2214</v>
+        <v>0.2774</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -548,13 +548,13 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>0.2325</v>
+        <v>0.2534</v>
       </c>
       <c r="F6" t="n">
         <v>0.319</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2006</v>
+        <v>0.2559</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -569,7 +569,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>0.204</v>
+        <v>0.2071</v>
       </c>
       <c r="G7" t="n">
         <v>0.2196</v>
@@ -638,7 +638,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>0.2663</v>
+        <v>0.3197</v>
       </c>
       <c r="F11" t="n">
         <v>0.2951</v>
@@ -770,22 +770,22 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>0.2292</v>
+        <v>0.2788</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2171</v>
+        <v>0.3083</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2024</v>
+        <v>0.2125</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2972</v>
+        <v>0.4113</v>
       </c>
       <c r="G19" t="n">
         <v>0.2093</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2187</v>
+        <v>0.3202</v>
       </c>
     </row>
     <row r="20">
@@ -872,7 +872,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>0.2049</v>
+        <v>0.3082</v>
       </c>
       <c r="H24" t="n">
         <v>0.2541</v>
@@ -886,22 +886,22 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>0.2225</v>
+        <v>0.4473</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2391</v>
+        <v>0.4463</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2019</v>
+        <v>0.3864</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2079</v>
+        <v>0.4264</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2106</v>
+        <v>0.4147</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2087</v>
+        <v>0.3831</v>
       </c>
     </row>
     <row r="26">
@@ -930,13 +930,13 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>0.2059</v>
+        <v>0.2257</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>0.2048</v>
+        <v>0.275</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0.2006</v>
+        <v>0.2035</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -1054,10 +1054,10 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.2789</v>
+        <v>0.3022</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2292</v>
+        <v>0.2461</v>
       </c>
     </row>
     <row r="35">
@@ -1070,16 +1070,16 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.2008</v>
+        <v>0.2323</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2108</v>
+        <v>0.2151</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2803</v>
+        <v>0.3963</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2614</v>
+        <v>0.3696</v>
       </c>
     </row>
     <row r="36">
@@ -1150,7 +1150,7 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0.2052</v>
+        <v>0.2254</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>0.2138</v>
+        <v>0.3016</v>
       </c>
       <c r="D40" t="n">
         <v>0.2077</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>0.2138</v>
+        <v>0.3114</v>
       </c>
       <c r="D42" t="n">
         <v>0.2668</v>
@@ -1222,10 +1222,10 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>0.3156</v>
+        <v>0.4259</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2077</v>
+        <v>0.2945</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
@@ -1264,10 +1264,10 @@
         <v>0.221</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2204</v>
+        <v>0.2504</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2352</v>
+        <v>0.2454</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         <v>0.2618</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2253</v>
+        <v>0.3615</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2106</v>
+        <v>0.2931</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1353,7 +1353,7 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>0.2087</v>
+        <v>0.2647</v>
       </c>
     </row>
     <row r="51">
@@ -1372,7 +1372,7 @@
         <v>0.2417</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2012</v>
+        <v>0.2107</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1390,7 +1390,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>0.2139</v>
+        <v>0.2228</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1402,16 +1402,16 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0.2198</v>
+        <v>0.2686</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2013</v>
+        <v>0.227</v>
       </c>
       <c r="E53" t="n">
         <v>0.2093</v>
       </c>
       <c r="F53" t="n">
-        <v>0.202</v>
+        <v>0.2074</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
         <v>0.3568</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2247</v>
+        <v>0.2298</v>
       </c>
       <c r="E54" t="n">
         <v>0.2613</v>
@@ -1436,7 +1436,7 @@
         <v>0.2373</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2155</v>
+        <v>0.2676</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1448,19 +1448,19 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>0.2002</v>
+        <v>0.2344</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2287</v>
+        <v>0.3063</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2241</v>
+        <v>0.2795</v>
       </c>
       <c r="F55" t="n">
         <v>0.2135</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2057</v>
+        <v>0.3132</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1478,7 +1478,7 @@
         <v>0.2163</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2029</v>
+        <v>0.2087</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1491,16 +1491,16 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
-        <v>0.2095</v>
+        <v>0.2367</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2388</v>
+        <v>0.3378</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2272</v>
+        <v>0.2413</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2155</v>
+        <v>0.2314</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1524,7 +1524,7 @@
         <v>0.2338</v>
       </c>
       <c r="G58" t="n">
-        <v>0.209</v>
+        <v>0.2174</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1535,19 +1535,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.2053</v>
+        <v>0.329</v>
       </c>
       <c r="C59" t="n">
-        <v>0.221</v>
+        <v>0.4063</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2166</v>
+        <v>0.2388</v>
       </c>
       <c r="E59" t="n">
-        <v>0.266</v>
+        <v>0.2905</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2078</v>
+        <v>0.2304</v>
       </c>
       <c r="G59" t="n">
         <v>0.2948</v>
@@ -1564,7 +1564,7 @@
         <v>0.2233</v>
       </c>
       <c r="C60" t="n">
-        <v>0.229</v>
+        <v>0.3665</v>
       </c>
       <c r="D60" t="n">
         <v>0.2155</v>
@@ -1587,7 +1587,7 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
-        <v>0.2262</v>
+        <v>0.3012</v>
       </c>
       <c r="E61" t="n">
         <v>0.2124</v>
@@ -1606,10 +1606,10 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0.2021</v>
+        <v>0.257</v>
       </c>
       <c r="D62" t="n">
-        <v>0.2363</v>
+        <v>0.2527</v>
       </c>
       <c r="E62" t="n">
         <v>0.242</v>
@@ -1710,19 +1710,19 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0.2338</v>
+        <v>0.3106</v>
       </c>
       <c r="D68" t="n">
-        <v>0.2335</v>
+        <v>0.2991</v>
       </c>
       <c r="E68" t="n">
         <v>0.2331</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2023</v>
+        <v>0.2899</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2386</v>
+        <v>0.2678</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -1735,13 +1735,13 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>0.2217</v>
+        <v>0.2797</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2019</v>
+        <v>0.2448</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2215</v>
+        <v>0.2405</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>0.2468</v>
+        <v>0.2799</v>
       </c>
       <c r="D70" t="n">
         <v>0.22</v>
@@ -1779,7 +1779,7 @@
         <v>0.3275</v>
       </c>
       <c r="D71" t="n">
-        <v>0.2142</v>
+        <v>0.4177</v>
       </c>
       <c r="E71" t="n">
         <v>0.2276</v>
@@ -1791,7 +1791,7 @@
         <v>0.3468</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2087</v>
+        <v>0.3263</v>
       </c>
     </row>
     <row r="72">
@@ -1814,7 +1814,7 @@
         <v>0.3308</v>
       </c>
       <c r="G72" t="n">
-        <v>0.2018</v>
+        <v>0.2577</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -1868,13 +1868,13 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>0.2617</v>
+        <v>0.3369</v>
       </c>
       <c r="D75" t="n">
-        <v>0.253</v>
+        <v>0.306</v>
       </c>
       <c r="E75" t="n">
-        <v>0.2925</v>
+        <v>0.3152</v>
       </c>
       <c r="F75" t="n">
         <v>0.207</v>
@@ -1907,7 +1907,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
-        <v>0.2401</v>
+        <v>0.2442</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
@@ -1932,7 +1932,7 @@
         <v>0.2398</v>
       </c>
       <c r="G78" t="n">
-        <v>0.2026</v>
+        <v>0.2215</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -1962,13 +1962,13 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>0.2133</v>
+        <v>0.2361</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2051</v>
+        <v>0.2434</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2125</v>
+        <v>0.2256</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
@@ -1982,16 +1982,16 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>0.2358</v>
+        <v>0.2393</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2198</v>
+        <v>0.2667</v>
       </c>
       <c r="E81" t="n">
-        <v>0.2399</v>
+        <v>0.2844</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2215</v>
+        <v>0.2295</v>
       </c>
       <c r="G81" t="n">
         <v>0.3326</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>0.2312</v>
+        <v>0.2455</v>
       </c>
       <c r="D82" t="n">
         <v>0.2005</v>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>0.2101</v>
+        <v>0.2752</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
@@ -2075,17 +2075,17 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.2046</v>
+        <v>0.2155</v>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="n">
-        <v>0.2262</v>
+        <v>0.2312</v>
       </c>
       <c r="E86" t="n">
-        <v>0.2132</v>
+        <v>0.2169</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2064</v>
+        <v>0.2621</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
@@ -2132,7 +2132,7 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>0.203</v>
+        <v>0.2116</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2164,13 +2164,13 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>0.2062</v>
+        <v>0.2494</v>
       </c>
       <c r="D91" t="n">
-        <v>0.2211</v>
+        <v>0.3012</v>
       </c>
       <c r="E91" t="n">
-        <v>0.2017</v>
+        <v>0.2265</v>
       </c>
       <c r="F91" t="n">
         <v>0.3281</v>
@@ -2185,19 +2185,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.2078</v>
+        <v>0.236</v>
       </c>
       <c r="C92" t="n">
         <v>0.2327</v>
       </c>
       <c r="D92" t="n">
-        <v>0.2226</v>
+        <v>0.3074</v>
       </c>
       <c r="E92" t="n">
-        <v>0.2069</v>
+        <v>0.2393</v>
       </c>
       <c r="F92" t="n">
-        <v>0.2204</v>
+        <v>0.3685</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
@@ -2215,7 +2215,7 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
-        <v>0.2042</v>
+        <v>0.2058</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
@@ -2237,7 +2237,7 @@
         <v>0.2808</v>
       </c>
       <c r="F94" t="n">
-        <v>0.2076</v>
+        <v>0.3427</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         <v>0.2632</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2094</v>
+        <v>0.3394</v>
       </c>
       <c r="G99" t="n">
-        <v>0.2427</v>
+        <v>0.2893</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2362,17 +2362,17 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>0.2485</v>
+        <v>0.2622</v>
       </c>
       <c r="D101" t="n">
-        <v>0.2341</v>
+        <v>0.247</v>
       </c>
       <c r="E101" t="n">
         <v>0.2375</v>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>0.2244</v>
+        <v>0.2487</v>
       </c>
       <c r="H101" t="n">
         <v>0.2638</v>
@@ -2401,16 +2401,16 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>0.2561</v>
+        <v>0.3796</v>
       </c>
       <c r="E103" t="n">
-        <v>0.2118</v>
+        <v>0.3268</v>
       </c>
       <c r="F103" t="n">
         <v>0.2801</v>
       </c>
       <c r="G103" t="n">
-        <v>0.2221</v>
+        <v>0.2519</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -2423,7 +2423,7 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>0.249</v>
+        <v>0.3065</v>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
@@ -2487,7 +2487,7 @@
         <v>0.2825</v>
       </c>
       <c r="D107" t="n">
-        <v>0.2445</v>
+        <v>0.2472</v>
       </c>
       <c r="E107" t="n">
         <v>0.2952</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="n">
-        <v>0.2091</v>
+        <v>0.2879</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
@@ -2578,7 +2578,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
-        <v>0.2109</v>
+        <v>0.2298</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -2657,7 +2657,7 @@
         <v>0.2429</v>
       </c>
       <c r="D117" t="n">
-        <v>0.202</v>
+        <v>0.2229</v>
       </c>
       <c r="E117" t="n">
         <v>0.2879</v>
@@ -2710,16 +2710,16 @@
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>0.2366</v>
+        <v>0.254</v>
       </c>
       <c r="D120" t="n">
         <v>0.2499</v>
       </c>
       <c r="E120" t="n">
-        <v>0.2353</v>
+        <v>0.3332</v>
       </c>
       <c r="F120" t="n">
-        <v>0.2199</v>
+        <v>0.2315</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="n">
-        <v>0.2019</v>
+        <v>0.303</v>
       </c>
       <c r="F124" t="n">
-        <v>0.2254</v>
+        <v>0.305</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
         <v>0.274</v>
       </c>
       <c r="D128" t="n">
-        <v>0.2035</v>
+        <v>0.2431</v>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="n">
-        <v>0.2382</v>
+        <v>0.2671</v>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
@@ -3025,7 +3025,7 @@
         <v>0.2014</v>
       </c>
       <c r="F139" t="n">
-        <v>0.2492</v>
+        <v>0.2622</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
@@ -3069,22 +3069,22 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.2015</v>
+        <v>0.3802</v>
       </c>
       <c r="C142" t="n">
-        <v>0.284</v>
+        <v>0.3965</v>
       </c>
       <c r="D142" t="n">
-        <v>0.2001</v>
+        <v>0.2212</v>
       </c>
       <c r="E142" t="n">
-        <v>0.2151</v>
+        <v>0.2635</v>
       </c>
       <c r="F142" t="n">
         <v>0.2576</v>
       </c>
       <c r="G142" t="n">
-        <v>0.2421</v>
+        <v>0.3088</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3098,13 +3098,13 @@
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="n">
-        <v>0.2403</v>
+        <v>0.2766</v>
       </c>
       <c r="F143" t="n">
         <v>0.3281</v>
       </c>
       <c r="G143" t="n">
-        <v>0.2843</v>
+        <v>0.3012</v>
       </c>
       <c r="H143" t="n">
         <v>0.3822</v>
@@ -3174,7 +3174,7 @@
         <v>0.2561</v>
       </c>
       <c r="E147" t="n">
-        <v>0.2116</v>
+        <v>0.2312</v>
       </c>
       <c r="F147" t="n">
         <v>0.2301</v>
